--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R42dedc07059a43ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R920a678d2f564aae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -418,7 +418,7 @@
         <x:v>详情与键盘</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
-        <x:v>滚动后打开C1027并读取transcript_count；连续Tab到达五个规定控件，在C1011按Enter打开详情</x:v>
+        <x:v>根据detail_target打开会话并读取transcript_count；使用Tab访问题面规定的控件，按Enter打开获得焦点的会话</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
@@ -429,12 +429,12 @@
         <x:v>浏览器时区使用Asia/Shanghai，时钟固定为2026-06-18T01:30:00Z，SLA分钟值不读取本机当前时间</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="48" customHeight="1">
+    <x:row r="16" ht="33" customHeight="1">
       <x:c r="A16" s="5" t="str">
         <x:v>截图内容</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
-        <x:v>截图取自CASE_AGENT_MINE_BILLING完成S01至S03后，依次显示C1011、C1008、C1030和C1022</x:v>
+        <x:v>截图取自坐席完成指定事件回放后的billing队列，页面会话顺序应与案例报告一致</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
@@ -442,15 +442,15 @@
         <x:v>完成条件</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
-        <x:v>npm run test:e2e返回0，六个目标路径存在，五个case_id均有结果，三份报告能按case_id、event_id和conversation_id互相对照</x:v>
+        <x:v>运行入口生成题面所列报告和截图，三份报告能够按case_id、event_id和conversation_id互相对照</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
       <x:c r="A18" s="5" t="str">
-        <x:v>可验证点</x:v>
+        <x:v>业务核对点</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>真实Chromium进程、REST路由、WebSocket message、两个角色集合、事件后排序、C1027详情、五步焦点、两条SLA和截图内容</x:v>
+        <x:v>Chromium进程、REST路由、WebSocket message、角色范围、事件后排序、会话详情、键盘焦点、SLA和截图内容</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R920a678d2f564aae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rf2a034b471af4eae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -346,20 +346,20 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>虚构客服工作台页面、脱敏会话、角色权限、Socket事件和发布场景</x:v>
+        <x:v>本次客服工作台发布批次的本地页面、会话、角色权限、Socket事件和业务场景，客户字段已脱敏</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="33" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>业务目标</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>解压输入数据包后在input_data目录读取本地文件，正式运行只访问本机静态服务</x:v>
+        <x:v>让发布负责人掌握不同角色的会话范围、事件后排序、会话详情、SLA文案和键盘焦点路径</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="78" customHeight="1">
       <x:c r="A7" s="5" t="str">
-        <x:v>原始输入文件</x:v>
+        <x:v>输入文件</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
         <x:v>app/support_console.html；app/support_console.js；fixtures/conversations.json；fixtures/socket_feed.json；fixtures/agent_roles.json；cases/realtime_cases.csv；rules/console_contract.json</x:v>
@@ -367,7 +367,7 @@
     </x:row>
     <x:row r="8" ht="78" customHeight="1">
       <x:c r="A8" s="5" t="str">
-        <x:v>目标输出文件</x:v>
+        <x:v>交付文件</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
         <x:v>playwright.config.ts；tests/support_console_realtime.spec.ts；reports/case_results.csv；reports/socket_event_audit.csv；reports/focus_path.csv；artifacts/agent-billing-after-feed.png</x:v>
@@ -375,90 +375,90 @@
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>角色范围</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>读取角色、会话、事件和场景；按权限计算路由数据；启动Chromium；回放Socket；操作队列、详情和键盘；记录浏览器观察值并保存截图</x:v>
+        <x:v>frontline-agent只看agent-a或未分配且属于授权队列的会话；queue-manager可以跨坐席查看授权队列</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
       <x:c r="A10" s="5" t="str">
-        <x:v>角色范围</x:v>
+        <x:v>REST路由</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>frontline-agent只看agent-a或未分配且属于授权队列的会话；queue-manager可以跨坐席查看授权队列</x:v>
+        <x:v>使用page.route接管/api/conversations，响应由角色、queue和priority字段计算，不改写原始fixture</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
       <x:c r="A11" s="5" t="str">
-        <x:v>REST路由</x:v>
+        <x:v>Socket回放</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>使用page.route接管/api/conversations，响应由角色、queue和priority字段计算，不改写原始fixture</x:v>
+        <x:v>在page.goto前通过page.addInitScript替换WebSocket，按S01至S04顺序发送message事件</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
       <x:c r="A12" s="5" t="str">
-        <x:v>Socket回放</x:v>
+        <x:v>排序规则</x:v>
       </x:c>
       <x:c r="B12" s="5" t="str">
-        <x:v>在page.goto前通过page.addInitScript替换WebSocket，按S01至S04顺序发送message事件</x:v>
+        <x:v>会话先按P1、P2、P3，再按first_response_due_utc和conversation_id升序</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
       <x:c r="A13" s="5" t="str">
-        <x:v>排序规则</x:v>
+        <x:v>详情与键盘</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>会话先按P1、P2、P3，再按first_response_due_utc和conversation_id升序</x:v>
+        <x:v>根据detail_target打开会话并读取transcript_count；使用Tab访问题面规定的控件，按Enter打开获得焦点的会话</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
       <x:c r="A14" s="5" t="str">
-        <x:v>详情与键盘</x:v>
+        <x:v>时区与时刻</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
-        <x:v>根据detail_target打开会话并读取transcript_count；使用Tab访问题面规定的控件，按Enter打开获得焦点的会话</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="48" customHeight="1">
+        <x:v>浏览器时区使用Asia/Shanghai，时钟固定为2026-06-18T01:30:00Z，SLA分钟值不读取本机当前时间</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="33" customHeight="1">
       <x:c r="A15" s="5" t="str">
-        <x:v>时区与时刻</x:v>
+        <x:v>截图内容</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>浏览器时区使用Asia/Shanghai，时钟固定为2026-06-18T01:30:00Z，SLA分钟值不读取本机当前时间</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="33" customHeight="1">
+        <x:v>截图取自坐席完成指定事件回放后的billing队列，页面会话顺序应与案例报告一致</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="48" customHeight="1">
       <x:c r="A16" s="5" t="str">
-        <x:v>截图内容</x:v>
+        <x:v>报告关联</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
-        <x:v>截图取自坐席完成指定事件回放后的billing队列，页面会话顺序应与案例报告一致</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="48" customHeight="1">
+        <x:v>案例报告以case_id为主键，事件报告通过event_id和conversation_id关联输入，焦点报告按order_index记录键盘路径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="33" customHeight="1">
       <x:c r="A17" s="5" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>截图交接</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
-        <x:v>运行入口生成题面所列报告和截图，三份报告能够按case_id、event_id和conversation_id互相对照</x:v>
+        <x:v>截图取自坐席完成指定Socket事件后的billing队列，页面会话顺序与案例报告一致</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
       <x:c r="A18" s="5" t="str">
-        <x:v>业务核对点</x:v>
+        <x:v>运行入口</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>Chromium进程、REST路由、WebSocket message、角色范围、事件后排序、会话详情、键盘焦点、SLA和截图内容</x:v>
+        <x:v>在input_data目录执行npm run test:e2e，由Playwright启动Chromium并生成报告和截图</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
       <x:c r="A19" s="5" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
-        <x:v>辅助函数拆分、变量名、注释风格、等价稳定locator、CSV必要引号、LF或CRLF行尾、本机回环端口和PNG压缩差异</x:v>
+        <x:v>可以调整辅助函数、变量名和等价稳定locator；角色范围、事件顺序、排序键、会话详情和键盘路径必须由Chromium页面交互得出</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
